--- a/tables/rf_values.xlsx
+++ b/tables/rf_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8F3E13-E79D-E34E-A788-4179C6EA1C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B8FD3F-018A-384F-AE8D-109358B47DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16800" yWindow="3920" windowWidth="27640" windowHeight="16940" xr2:uid="{F072C06C-3E8C-714E-B4AA-715B8439311A}"/>
   </bookViews>
